--- a/jogos_2024-09-11.xlsx
+++ b/jogos_2024-09-11.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIS Semarang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['18', '43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.83</v>
+        <v>2.39</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45546.22916666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSIS Semarang</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AD4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '43']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.84</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45546.22916666666</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Memphis 901</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
@@ -2112,59 +2112,59 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['36', '86']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.24</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45546.875</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Memphis 901</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
@@ -2241,41 +2241,41 @@
         <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['36', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45546.875</v>
